--- a/artfynd/S 1527-2024 artfynd.xlsx
+++ b/artfynd/S 1527-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136317688</v>
       </c>
       <c r="B3" t="n">
-        <v>104062</v>
+        <v>104065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1527-2024 artfynd.xlsx
+++ b/artfynd/S 1527-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136317688</v>
       </c>
       <c r="B3" t="n">
-        <v>104065</v>
+        <v>104066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1527-2024 artfynd.xlsx
+++ b/artfynd/S 1527-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136317688</v>
       </c>
       <c r="B3" t="n">
-        <v>104066</v>
+        <v>104071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1527-2024 artfynd.xlsx
+++ b/artfynd/S 1527-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136317688</v>
       </c>
       <c r="B3" t="n">
-        <v>104071</v>
+        <v>104073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1527-2024 artfynd.xlsx
+++ b/artfynd/S 1527-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136317688</v>
       </c>
       <c r="B3" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
